--- a/min_heterogeneity.xlsx
+++ b/min_heterogeneity.xlsx
@@ -1169,7 +1169,7 @@
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
